--- a/Files/rajdhani-day-penal-chart.xlsx
+++ b/Files/rajdhani-day-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$460</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$462</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2402,6 +2402,12 @@
   </x:si>
   <x:si>
     <x:t>31/08/2026 to 05/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07/09/2026 to 12/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14/09/2026 to 19/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2857,7 +2863,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V460"/>
+  <x:dimension ref="A1:V462"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -34090,49 +34096,49 @@
         <x:v>66</x:v>
       </x:c>
       <x:c r="E460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="F460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="H460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="I460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="J460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="K460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="L460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="M460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="N460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="O460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="P460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="Q460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="R460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="S460" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="T460" s="3" t="s">
         <x:v>41</x:v>
@@ -34144,8 +34150,144 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="461" spans="1:22">
+      <x:c r="A461" s="3" t="s">
+        <x:v>795</x:v>
+      </x:c>
+      <x:c r="B461" s="3" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="C461" s="3" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="D461" s="3" t="s">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="E461" s="3" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="F461" s="3" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="G461" s="3" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="H461" s="3" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="I461" s="3" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="J461" s="3" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="K461" s="3" t="s">
+        <x:v>304</x:v>
+      </x:c>
+      <x:c r="L461" s="3" t="s">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="M461" s="3" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="N461" s="3" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="O461" s="3" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="P461" s="3" t="s">
+        <x:v>229</x:v>
+      </x:c>
+      <x:c r="Q461" s="3" t="s">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="R461" s="3" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="S461" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="T461" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U461" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V461" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="462" spans="1:22">
+      <x:c r="A462" s="3" t="s">
+        <x:v>796</x:v>
+      </x:c>
+      <x:c r="B462" s="3" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="C462" s="3" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="D462" s="3" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="E462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="F462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="G462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="J462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="K462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="L462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="M462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="N462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V462" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V460"/>
+  <x:autoFilter ref="A1:V462"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -34168,39 +34310,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>795</x:v>
+        <x:v>797</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>796</x:v>
+        <x:v>798</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>797</x:v>
+        <x:v>799</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>798</x:v>
+        <x:v>800</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>799</x:v>
+        <x:v>801</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>800</x:v>
+        <x:v>802</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>801</x:v>
+        <x:v>803</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>459</x:v>
+        <x:v>461</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>802</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -34208,10 +34350,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>803</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>794</x:v>
+        <x:v>796</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/Files/rajdhani-day-penal-chart.xlsx
+++ b/Files/rajdhani-day-penal-chart.xlsx
@@ -10,7 +10,7 @@
     <x:sheet name="Source" sheetId="2" r:id="rId3"/>
   </x:sheets>
   <x:definedNames>
-    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$462</x:definedName>
+    <x:definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Data!$A$1:$V$463</x:definedName>
   </x:definedNames>
   <x:calcPr calcId="125725"/>
 </x:workbook>
@@ -2408,6 +2408,9 @@
   </x:si>
   <x:si>
     <x:t>14/09/2026 to 19/09/2026</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21/09/2026 to 26/09/2026</x:t>
   </x:si>
   <x:si>
     <x:t>Field</x:t>
@@ -2863,7 +2866,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:V462"/>
+  <x:dimension ref="A1:V463"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="28.710625" style="0" customWidth="1"/>
@@ -34232,49 +34235,49 @@
         <x:v>37</x:v>
       </x:c>
       <x:c r="E462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="F462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="H462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="I462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="J462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="K462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="M462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="N462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="O462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="P462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="Q462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="R462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="S462" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>268</x:v>
       </x:c>
       <x:c r="T462" s="3" t="s">
         <x:v>41</x:v>
@@ -34286,8 +34289,76 @@
         <x:v>41</x:v>
       </x:c>
     </x:row>
+    <x:row r="463" spans="1:22">
+      <x:c r="A463" s="3" t="s">
+        <x:v>797</x:v>
+      </x:c>
+      <x:c r="B463" s="3" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C463" s="3" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D463" s="3" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E463" s="3" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="F463" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G463" s="3" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="H463" s="3" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I463" s="3" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="J463" s="3" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="K463" s="3" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="L463" s="3" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="M463" s="3" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="N463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="O463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="P463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="Q463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="R463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="S463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="T463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="U463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="V463" s="3" t="s">
+        <x:v>41</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A1:V462"/>
+  <x:autoFilter ref="A1:V463"/>
   <x:printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0"/>
   <x:pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
@@ -34310,39 +34381,39 @@
   <x:sheetData>
     <x:row r="1" spans="1:2">
       <x:c r="A1" s="4" t="s">
-        <x:v>797</x:v>
+        <x:v>798</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>798</x:v>
+        <x:v>799</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:2">
       <x:c r="A2" s="5" t="s">
-        <x:v>799</x:v>
+        <x:v>800</x:v>
       </x:c>
       <x:c r="B2" s="6" t="s">
-        <x:v>800</x:v>
+        <x:v>801</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:2">
       <x:c r="A3" s="5" t="s">
-        <x:v>801</x:v>
+        <x:v>802</x:v>
       </x:c>
       <x:c r="B3" s="6" t="s">
-        <x:v>802</x:v>
+        <x:v>803</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:2">
       <x:c r="A4" s="5" t="s">
-        <x:v>803</x:v>
+        <x:v>804</x:v>
       </x:c>
       <x:c r="B4" s="6">
-        <x:v>461</x:v>
+        <x:v>462</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:2">
       <x:c r="A5" s="5" t="s">
-        <x:v>804</x:v>
+        <x:v>805</x:v>
       </x:c>
       <x:c r="B5" s="6" t="s">
         <x:v>22</x:v>
@@ -34350,10 +34421,10 @@
     </x:row>
     <x:row r="6" spans="1:2">
       <x:c r="A6" s="5" t="s">
-        <x:v>805</x:v>
+        <x:v>806</x:v>
       </x:c>
       <x:c r="B6" s="6" t="s">
-        <x:v>796</x:v>
+        <x:v>797</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
